--- a/public/samples/en/sample1.xlsx
+++ b/public/samples/en/sample1.xlsx
@@ -1063,7 +1063,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>Owen Wilson</v>
+        <v>Caleb Campbell</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>M</v>
@@ -1092,16 +1092,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>Harper Walker</v>
+        <v>Harper Baker</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D23" s="2">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1121,13 +1121,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>Caleb Campbell</v>
+        <v>Ryan White</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D24" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2">
         <v>3</v>
@@ -1150,13 +1150,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>Ella Thompson</v>
+        <v>Ella Anderson</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D25" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2">
         <v>2</v>
@@ -1179,16 +1179,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>Ryan Thompson</v>
+        <v>Isaac Nelson</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D26" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E26" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1208,16 +1208,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>Ruby Brown</v>
+        <v>Ruby Smith</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D27" s="2">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="I27" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="28">
@@ -1237,13 +1237,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>Isaac Nelson</v>
+        <v>Samuel Nelson</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D28" s="2">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
@@ -1266,13 +1266,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>Aria Wright</v>
+        <v>Aria Adams</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D29" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2">
         <v>3</v>
@@ -1295,16 +1295,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>Samuel Green</v>
+        <v>Daniel Wilson</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D30" s="2">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1324,13 +1324,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>Nora Taylor</v>
+        <v>Nora Brown</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D31" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
@@ -1353,13 +1353,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>Daniel Johnson</v>
+        <v>Aiden White</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D32" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2">
         <v>2</v>
@@ -1374,7 +1374,7 @@
         <v/>
       </c>
       <c r="I32" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="33">
@@ -1382,16 +1382,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>Maya Thompson</v>
+        <v>Maya Johnson</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D33" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E33" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1411,16 +1411,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>Aiden Smith</v>
+        <v>Max Hill</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D34" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
       <c r="I34" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="35">
@@ -1440,16 +1440,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>Leah Anderson</v>
+        <v>Leah Baker</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D35" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>Max Baker</v>
+        <v>Theo Martin</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D36" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E36" s="2">
         <v>2</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G36" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H36" s="2" t="str">
         <v/>
@@ -1498,16 +1498,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>Ivy Wright</v>
+        <v>Ivy White</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D37" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="2" t="str">
         <v/>
@@ -1516,10 +1516,10 @@
         <v/>
       </c>
       <c r="H37" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I37" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -1527,22 +1527,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>Theo Baker</v>
+        <v>Jacob Taylor</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D38" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="G38" s="2" t="str">
-        <v/>
       </c>
       <c r="H38" s="2" t="str">
         <v/>
@@ -1556,13 +1556,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>Hannah Nelson</v>
+        <v>Hannah Martin</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D39" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E39" s="2">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         <v/>
       </c>
       <c r="G39" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H39" s="2" t="str">
         <v/>
@@ -1585,13 +1585,13 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>Jacob Green</v>
+        <v>Eli Young</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D40" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2">
         <v>2</v>
@@ -1614,7 +1614,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>Amelia Campbell</v>
+        <v>Amelia Brown</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>F</v>
@@ -1623,16 +1623,16 @@
         <v>69</v>
       </c>
       <c r="E41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
         <v>✓</v>
       </c>
-      <c r="G41" s="2" t="str">
-        <v/>
-      </c>
       <c r="H41" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="I41" s="2" t="str">
         <v/>
@@ -1643,28 +1643,28 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>Eli Brown</v>
+        <v>Liam Johnson</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D42" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I42" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="G42" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H42" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I42" s="2" t="str">
-        <v/>
       </c>
     </row>
     <row r="43">
@@ -1672,16 +1672,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>Emma Scott</v>
+        <v>Emma Taylor</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D43" s="2">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1701,16 +1701,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>Liam Adams</v>
+        <v>Noah Hill</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D44" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1736,10 +1736,10 @@
         <v>F</v>
       </c>
       <c r="D45" s="2">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1759,19 +1759,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>Noah Taylor</v>
+        <v>Oliver Smith</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D46" s="2">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G46" s="2" t="str">
         <v/>
@@ -1780,7 +1780,7 @@
         <v/>
       </c>
       <c r="I46" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1788,28 +1788,28 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>Ava Johnson</v>
+        <v>Ava Wilson</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D47" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I47" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="G47" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H47" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I47" s="2" t="str">
-        <v/>
       </c>
     </row>
     <row r="48">
@@ -1817,13 +1817,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>Oliver Hill</v>
+        <v>Ethan King</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D48" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
@@ -1846,13 +1846,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>Sophia Wright</v>
+        <v>Sophia Baker</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D49" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2">
         <v>2</v>
@@ -1875,22 +1875,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>Ethan King</v>
+        <v>Lucas Young</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D50" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
       </c>
       <c r="G50" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H50" s="2" t="str">
         <v/>
@@ -1904,13 +1904,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>Mia Green</v>
+        <v>Mia Wilson</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D51" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E51" s="2">
         <v>3</v>
@@ -1933,22 +1933,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>Lucas Scott</v>
+        <v>Mason Wright</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D52" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G52" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H52" s="2" t="str">
         <v/>
@@ -1962,19 +1962,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>Isla Martin</v>
+        <v>Isla Brown</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D53" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E53" s="2">
         <v>1</v>
       </c>
       <c r="F53" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G53" s="2" t="str">
         <v/>
@@ -1991,22 +1991,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>Mason Campbell</v>
+        <v>Jack Green</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D54" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="2" t="str">
         <v/>
       </c>
       <c r="G54" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H54" s="2" t="str">
         <v/>
@@ -2020,16 +2020,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>Grace Anderson</v>
+        <v>Grace Wilson</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D55" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2049,16 +2049,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>Jack Brown</v>
+        <v>Leo King</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D56" s="2">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2078,16 +2078,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>Chloe Martin</v>
+        <v>Chloe Brown</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D57" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="str">
         <v/>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="I57" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -2107,13 +2107,13 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Leo Wright</v>
+        <v>Henry Anderson</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D58" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E58" s="2">
         <v>2</v>
@@ -2136,28 +2136,28 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Lily Brown</v>
+        <v>Lily Walker</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D59" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E59" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G59" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="H59" s="2" t="str">
         <v/>
       </c>
       <c r="I59" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2165,7 +2165,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Henry Walker</v>
+        <v>Owen Smith</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>M</v>
@@ -2180,10 +2180,10 @@
         <v/>
       </c>
       <c r="G60" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="H60" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="I60" s="2" t="str">
         <v/>
@@ -2194,16 +2194,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Zoe Smith</v>
+        <v>Zoe King</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D61" s="2">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E61" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="I61" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
     </row>
     <row r="62">
@@ -2223,16 +2223,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Owen Martin</v>
+        <v>Caleb Wright</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D62" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2252,16 +2252,16 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Ruby Scott</v>
+        <v>Harper Thompson</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D63" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2281,16 +2281,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Caleb White</v>
+        <v>Ryan Anderson</v>
       </c>
       <c r="C64" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D64" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2310,22 +2310,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Aria Martin</v>
+        <v>Ella Taylor</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D65" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="G65" s="2" t="str">
-        <v/>
       </c>
       <c r="H65" s="2" t="str">
         <v/>
@@ -2339,25 +2339,25 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Ryan Smith</v>
+        <v>Isaac Baker</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D66" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G66" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H66" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="H66" s="2" t="str">
-        <v/>
       </c>
       <c r="I66" s="2" t="str">
         <v/>
@@ -2368,16 +2368,16 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Nora Nelson</v>
+        <v>Ruby Anderson</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D67" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2397,16 +2397,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Isaac Wright</v>
+        <v>Samuel Scott</v>
       </c>
       <c r="C68" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D68" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2426,16 +2426,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Maya Walker</v>
+        <v>Aria Hill</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D69" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2455,19 +2455,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Samuel Campbell</v>
+        <v>Daniel King</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D70" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G70" s="2" t="str">
         <v/>
@@ -2484,16 +2484,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Leah Scott</v>
+        <v>Nora Thompson</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D71" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E71" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2513,13 +2513,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Daniel Wilson</v>
+        <v>Aiden Thompson</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D72" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2">
         <v>2</v>
@@ -2542,13 +2542,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>Ivy Nelson</v>
+        <v>Maya Campbell</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D73" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E73" s="2">
         <v>2</v>
@@ -2571,22 +2571,22 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Aiden Wilson</v>
+        <v>Max Taylor</v>
       </c>
       <c r="C74" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D74" s="2">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2">
         <v>2</v>
       </c>
       <c r="F74" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="G74" s="2" t="str">
-        <v/>
       </c>
       <c r="H74" s="2" t="str">
         <v/>
@@ -2600,13 +2600,13 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>Hannah Thompson</v>
+        <v>Leah Taylor</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D75" s="2">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E75" s="2">
         <v>2</v>
@@ -2629,13 +2629,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Max Wright</v>
+        <v>Theo Nelson</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D76" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2">
         <v>2</v>
@@ -2658,13 +2658,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Amelia Thompson</v>
+        <v>Ivy Baker</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D77" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E77" s="2">
         <v>1</v>
@@ -2687,16 +2687,16 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Jacob Nelson</v>
+        <v>Jacob Anderson</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D78" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2716,28 +2716,28 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Emma Baker</v>
+        <v>Hannah Walker</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D79" s="2">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E79" s="2">
         <v>2</v>
       </c>
       <c r="F79" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="G79" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H79" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I79" s="2" t="str">
         <v>✓</v>
-      </c>
-      <c r="H79" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I79" s="2" t="str">
-        <v/>
       </c>
     </row>
     <row r="80">
@@ -2745,19 +2745,19 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Eli Young</v>
+        <v>Eli Scott</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D80" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
       <c r="G80" s="2" t="str">
         <v/>
@@ -2766,7 +2766,7 @@
         <v/>
       </c>
       <c r="I80" s="2" t="str">
-        <v>✓</v>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -2774,16 +2774,16 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Olivia Taylor</v>
+        <v>Amelia King</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>F</v>
       </c>
       <c r="D81" s="2">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E81" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" s="2" t="str">
         <v/>
@@ -2803,16 +2803,16 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Liam Johnson</v>
+        <v>Liam Young</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>M</v>
       </c>
       <c r="D82" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E82" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="str">
         <v/>
@@ -2840,37 +2840,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
+        <v>65</v>
+      </c>
+      <c r="B1" s="2">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2">
         <v>42</v>
-      </c>
-      <c r="B1" s="2">
-        <v>61</v>
-      </c>
-      <c r="C1" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2886,37 +2886,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2">
         <v>27</v>
-      </c>
-      <c r="B2" s="2">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/en/sample1.xlsx
+++ b/public/samples/en/sample1.xlsx
@@ -495,16 +495,16 @@
         <v>Math level</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>IEP/504 plan</v>
+        <v>Learning support</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>English learner</v>
+        <v>English support</v>
       </c>
       <c r="H2" s="2" t="str">
-        <v>Behavior support</v>
+        <v>Leadership</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>Leadership</v>
+        <v>Previous class</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
         <v>79</v>
       </c>
       <c r="E3" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="I3" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>✓</v>
       </c>
       <c r="I4" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="I5" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         <v>72</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -617,10 +617,10 @@
         <v/>
       </c>
       <c r="H6" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I6" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +637,7 @@
         <v>77</v>
       </c>
       <c r="E7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -649,7 +649,7 @@
         <v/>
       </c>
       <c r="I7" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="8">
@@ -660,13 +660,13 @@
         <v>Oliver Anderson</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D8" s="2">
         <v>82</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
@@ -678,7 +678,7 @@
         <v/>
       </c>
       <c r="I8" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="9">
@@ -704,10 +704,10 @@
         <v/>
       </c>
       <c r="H9" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I9" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="10">
@@ -724,7 +724,7 @@
         <v>92</v>
       </c>
       <c r="E10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="I10" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +753,7 @@
         <v>72</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -765,7 +765,7 @@
         <v/>
       </c>
       <c r="I11" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="12">
@@ -794,7 +794,7 @@
         <v/>
       </c>
       <c r="I12" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="13">
@@ -811,7 +811,7 @@
         <v>82</v>
       </c>
       <c r="E13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -823,7 +823,7 @@
         <v/>
       </c>
       <c r="I13" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
         <v>88</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
         <v/>
@@ -852,7 +852,7 @@
         <v/>
       </c>
       <c r="I14" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="15">
@@ -869,7 +869,7 @@
         <v>84</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="str">
         <v>✓</v>
@@ -881,7 +881,7 @@
         <v/>
       </c>
       <c r="I15" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="16">
@@ -898,7 +898,7 @@
         <v>61</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v>✓</v>
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="I16" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="17">
@@ -927,7 +927,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v/>
       </c>
       <c r="I17" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="18">
@@ -956,7 +956,7 @@
         <v>63</v>
       </c>
       <c r="E18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -968,7 +968,7 @@
         <v/>
       </c>
       <c r="I18" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="19">
@@ -994,10 +994,10 @@
         <v/>
       </c>
       <c r="H19" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I19" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="20">
@@ -1026,7 +1026,7 @@
         <v/>
       </c>
       <c r="I20" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="21">
@@ -1043,7 +1043,7 @@
         <v>76</v>
       </c>
       <c r="E21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -1055,7 +1055,7 @@
         <v/>
       </c>
       <c r="I21" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="22">
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="I22" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="23">
@@ -1101,7 +1101,7 @@
         <v>72</v>
       </c>
       <c r="E23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1113,7 +1113,7 @@
         <v/>
       </c>
       <c r="I23" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="24">
@@ -1130,7 +1130,7 @@
         <v>82</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1142,7 +1142,7 @@
         <v/>
       </c>
       <c r="I24" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="25">
@@ -1159,7 +1159,7 @@
         <v>79</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1171,7 +1171,7 @@
         <v/>
       </c>
       <c r="I25" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="26">
@@ -1188,7 +1188,7 @@
         <v>94</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1200,7 +1200,7 @@
         <v/>
       </c>
       <c r="I26" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="27">
@@ -1217,7 +1217,7 @@
         <v>60</v>
       </c>
       <c r="E27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="I27" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="28">
@@ -1246,7 +1246,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1258,7 +1258,7 @@
         <v/>
       </c>
       <c r="I28" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="29">
@@ -1275,7 +1275,7 @@
         <v>83</v>
       </c>
       <c r="E29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="str">
         <v/>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="I29" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="30">
@@ -1304,7 +1304,7 @@
         <v>65</v>
       </c>
       <c r="E30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v/>
       </c>
       <c r="I30" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="31">
@@ -1333,7 +1333,7 @@
         <v>76</v>
       </c>
       <c r="E31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -1345,7 +1345,7 @@
         <v/>
       </c>
       <c r="I31" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="32">
@@ -1374,7 +1374,7 @@
         <v/>
       </c>
       <c r="I32" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="33">
@@ -1391,7 +1391,7 @@
         <v>76</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1403,7 +1403,7 @@
         <v/>
       </c>
       <c r="I33" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="34">
@@ -1414,7 +1414,7 @@
         <v>Max Hill</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D34" s="2">
         <v>76</v>
@@ -1432,7 +1432,7 @@
         <v/>
       </c>
       <c r="I34" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="35">
@@ -1449,7 +1449,7 @@
         <v>87</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="I35" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="36">
@@ -1478,7 +1478,7 @@
         <v>88</v>
       </c>
       <c r="E36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
         <v>✓</v>
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="I36" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="37">
@@ -1507,7 +1507,7 @@
         <v>79</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2" t="str">
         <v/>
@@ -1519,7 +1519,7 @@
         <v>✓</v>
       </c>
       <c r="I37" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="38">
@@ -1548,7 +1548,7 @@
         <v/>
       </c>
       <c r="I38" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="39">
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="I39" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="40">
@@ -1594,7 +1594,7 @@
         <v>85</v>
       </c>
       <c r="E40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="I40" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="41">
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="I41" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="42">
@@ -1664,7 +1664,7 @@
         <v/>
       </c>
       <c r="I42" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="43">
@@ -1681,7 +1681,7 @@
         <v>70</v>
       </c>
       <c r="E43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v/>
       </c>
       <c r="I43" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="44">
@@ -1710,7 +1710,7 @@
         <v>82</v>
       </c>
       <c r="E44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="I44" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="45">
@@ -1739,7 +1739,7 @@
         <v>72</v>
       </c>
       <c r="E45" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1751,7 +1751,7 @@
         <v/>
       </c>
       <c r="I45" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="46">
@@ -1777,10 +1777,10 @@
         <v/>
       </c>
       <c r="H46" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I46" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="47">
@@ -1809,7 +1809,7 @@
         <v/>
       </c>
       <c r="I47" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="48">
@@ -1826,7 +1826,7 @@
         <v>83</v>
       </c>
       <c r="E48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="I48" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="49">
@@ -1855,7 +1855,7 @@
         <v>89</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1867,7 +1867,7 @@
         <v/>
       </c>
       <c r="I49" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="50">
@@ -1884,7 +1884,7 @@
         <v>72</v>
       </c>
       <c r="E50" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
@@ -1896,7 +1896,7 @@
         <v/>
       </c>
       <c r="I50" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="51">
@@ -1913,7 +1913,7 @@
         <v>88</v>
       </c>
       <c r="E51" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
@@ -1925,7 +1925,7 @@
         <v/>
       </c>
       <c r="I51" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="52">
@@ -1942,7 +1942,7 @@
         <v>74</v>
       </c>
       <c r="E52" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
         <v>✓</v>
@@ -1954,7 +1954,7 @@
         <v/>
       </c>
       <c r="I52" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="53">
@@ -1983,7 +1983,7 @@
         <v/>
       </c>
       <c r="I53" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="54">
@@ -2000,7 +2000,7 @@
         <v>84</v>
       </c>
       <c r="E54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="str">
         <v/>
@@ -2012,7 +2012,7 @@
         <v/>
       </c>
       <c r="I54" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="55">
@@ -2029,7 +2029,7 @@
         <v>88</v>
       </c>
       <c r="E55" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v/>
       </c>
       <c r="I55" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="56">
@@ -2058,7 +2058,7 @@
         <v>68</v>
       </c>
       <c r="E56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2070,7 +2070,7 @@
         <v/>
       </c>
       <c r="I56" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="57">
@@ -2096,10 +2096,10 @@
         <v/>
       </c>
       <c r="H57" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I57" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="58">
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="I58" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="59">
@@ -2145,7 +2145,7 @@
         <v>70</v>
       </c>
       <c r="E59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
         <v>✓</v>
@@ -2154,10 +2154,10 @@
         <v/>
       </c>
       <c r="H59" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I59" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="60">
@@ -2168,13 +2168,13 @@
         <v>Owen Smith</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D60" s="2">
         <v>82</v>
       </c>
       <c r="E60" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
@@ -2186,7 +2186,7 @@
         <v/>
       </c>
       <c r="I60" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="61">
@@ -2203,7 +2203,7 @@
         <v>74</v>
       </c>
       <c r="E61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="I61" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="62">
@@ -2232,7 +2232,7 @@
         <v>85</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2244,7 +2244,7 @@
         <v/>
       </c>
       <c r="I62" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="63">
@@ -2261,7 +2261,7 @@
         <v>62</v>
       </c>
       <c r="E63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2273,7 +2273,7 @@
         <v/>
       </c>
       <c r="I63" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="64">
@@ -2290,7 +2290,7 @@
         <v>78</v>
       </c>
       <c r="E64" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2302,7 +2302,7 @@
         <v/>
       </c>
       <c r="I64" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="65">
@@ -2319,7 +2319,7 @@
         <v>78</v>
       </c>
       <c r="E65" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2331,7 +2331,7 @@
         <v/>
       </c>
       <c r="I65" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="66">
@@ -2348,7 +2348,7 @@
         <v>70</v>
       </c>
       <c r="E66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="str">
         <v>✓</v>
@@ -2360,7 +2360,7 @@
         <v>✓</v>
       </c>
       <c r="I66" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="67">
@@ -2377,7 +2377,7 @@
         <v>70</v>
       </c>
       <c r="E67" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="I67" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="68">
@@ -2406,7 +2406,7 @@
         <v>77</v>
       </c>
       <c r="E68" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="I68" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="69">
@@ -2435,7 +2435,7 @@
         <v>85</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2447,7 +2447,7 @@
         <v/>
       </c>
       <c r="I69" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="70">
@@ -2464,7 +2464,7 @@
         <v>83</v>
       </c>
       <c r="E70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v>✓</v>
@@ -2476,7 +2476,7 @@
         <v/>
       </c>
       <c r="I70" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="71">
@@ -2493,7 +2493,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2505,7 +2505,7 @@
         <v/>
       </c>
       <c r="I71" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="72">
@@ -2534,7 +2534,7 @@
         <v/>
       </c>
       <c r="I72" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -2551,7 +2551,7 @@
         <v>73</v>
       </c>
       <c r="E73" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
         <v/>
@@ -2563,7 +2563,7 @@
         <v/>
       </c>
       <c r="I73" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="74">
@@ -2592,7 +2592,7 @@
         <v/>
       </c>
       <c r="I74" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="75">
@@ -2609,7 +2609,7 @@
         <v>68</v>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
         <v/>
@@ -2621,7 +2621,7 @@
         <v/>
       </c>
       <c r="I75" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="76">
@@ -2638,7 +2638,7 @@
         <v>77</v>
       </c>
       <c r="E76" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2650,7 +2650,7 @@
         <v/>
       </c>
       <c r="I76" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="77">
@@ -2667,7 +2667,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
@@ -2679,7 +2679,7 @@
         <v/>
       </c>
       <c r="I77" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="78">
@@ -2696,7 +2696,7 @@
         <v>89</v>
       </c>
       <c r="E78" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="I78" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="79">
@@ -2725,7 +2725,7 @@
         <v>93</v>
       </c>
       <c r="E79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
         <v>✓</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="I79" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="80">
@@ -2763,10 +2763,10 @@
         <v/>
       </c>
       <c r="H80" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I80" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="81">
@@ -2795,7 +2795,7 @@
         <v/>
       </c>
       <c r="I81" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2824,7 +2824,7 @@
         <v/>
       </c>
       <c r="I82" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/en/sample1.xlsx
+++ b/public/samples/en/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Roster" sheetId="2" r:id="rId2"/>
     <sheet name="Keep together" sheetId="3" r:id="rId3"/>
     <sheet name="Keep apart" sheetId="4" r:id="rId4"/>
+    <sheet name="Attributes" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -660,7 +661,7 @@
         <v>Oliver Anderson</v>
       </c>
       <c r="C8" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D8" s="2">
         <v>82</v>
@@ -892,7 +893,7 @@
         <v>Jack Wright</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D16" s="2">
         <v>61</v>
@@ -1414,7 +1415,7 @@
         <v>Max Hill</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D34" s="2">
         <v>76</v>
@@ -1675,7 +1676,7 @@
         <v>Emma Taylor</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
@@ -2168,7 +2169,7 @@
         <v>Owen Smith</v>
       </c>
       <c r="C60" s="2" t="str">
-        <v>X</v>
+        <v>M</v>
       </c>
       <c r="D60" s="2">
         <v>82</v>
@@ -2429,7 +2430,7 @@
         <v>Aria Hill</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D69" s="2">
         <v>85</v>
@@ -2924,4 +2925,103 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Attribute</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Options</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Reading score</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Number</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Math level</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Scale</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>English support</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Leadership</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>Previous class</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/en/sample1.xlsx
+++ b/public/samples/en/sample1.xlsx
@@ -7,6 +7,7 @@
     <sheet name="Roster" sheetId="2" r:id="rId2"/>
     <sheet name="Keep together" sheetId="3" r:id="rId3"/>
     <sheet name="Keep apart" sheetId="4" r:id="rId4"/>
+    <sheet name="Attributes" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -495,16 +496,16 @@
         <v>Math level</v>
       </c>
       <c r="F2" s="2" t="str">
-        <v>IEP/504 plan</v>
+        <v>Learning support</v>
       </c>
       <c r="G2" s="2" t="str">
-        <v>English learner</v>
+        <v>English support</v>
       </c>
       <c r="H2" s="2" t="str">
-        <v>Behavior support</v>
+        <v>Leadership</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>Leadership</v>
+        <v>Previous class</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +522,7 @@
         <v>79</v>
       </c>
       <c r="E3" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
         <v/>
@@ -533,7 +534,7 @@
         <v/>
       </c>
       <c r="I3" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +563,7 @@
         <v>✓</v>
       </c>
       <c r="I4" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +592,7 @@
         <v/>
       </c>
       <c r="I5" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +609,7 @@
         <v>72</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
         <v/>
@@ -617,10 +618,10 @@
         <v/>
       </c>
       <c r="H6" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I6" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +638,7 @@
         <v>77</v>
       </c>
       <c r="E7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="str">
         <v/>
@@ -649,7 +650,7 @@
         <v/>
       </c>
       <c r="I7" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="8">
@@ -666,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="E8" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="str">
         <v/>
@@ -678,7 +679,7 @@
         <v/>
       </c>
       <c r="I8" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="9">
@@ -704,10 +705,10 @@
         <v/>
       </c>
       <c r="H9" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I9" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="10">
@@ -724,7 +725,7 @@
         <v>92</v>
       </c>
       <c r="E10" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="str">
         <v/>
@@ -736,7 +737,7 @@
         <v/>
       </c>
       <c r="I10" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +754,7 @@
         <v>72</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
         <v/>
@@ -765,7 +766,7 @@
         <v/>
       </c>
       <c r="I11" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="12">
@@ -794,7 +795,7 @@
         <v/>
       </c>
       <c r="I12" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="13">
@@ -811,7 +812,7 @@
         <v>82</v>
       </c>
       <c r="E13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
         <v/>
@@ -823,7 +824,7 @@
         <v/>
       </c>
       <c r="I13" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +841,7 @@
         <v>88</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
         <v/>
@@ -852,7 +853,7 @@
         <v/>
       </c>
       <c r="I14" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="15">
@@ -869,7 +870,7 @@
         <v>84</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="str">
         <v>✓</v>
@@ -881,7 +882,7 @@
         <v/>
       </c>
       <c r="I15" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="16">
@@ -892,13 +893,13 @@
         <v>Jack Wright</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>M</v>
+        <v>X</v>
       </c>
       <c r="D16" s="2">
         <v>61</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="str">
         <v>✓</v>
@@ -910,7 +911,7 @@
         <v/>
       </c>
       <c r="I16" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="17">
@@ -927,7 +928,7 @@
         <v>97</v>
       </c>
       <c r="E17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="str">
         <v/>
@@ -939,7 +940,7 @@
         <v/>
       </c>
       <c r="I17" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="18">
@@ -956,7 +957,7 @@
         <v>63</v>
       </c>
       <c r="E18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="2" t="str">
         <v/>
@@ -968,7 +969,7 @@
         <v/>
       </c>
       <c r="I18" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="19">
@@ -994,10 +995,10 @@
         <v/>
       </c>
       <c r="H19" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I19" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="20">
@@ -1026,7 +1027,7 @@
         <v/>
       </c>
       <c r="I20" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="21">
@@ -1043,7 +1044,7 @@
         <v>76</v>
       </c>
       <c r="E21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
         <v/>
@@ -1055,7 +1056,7 @@
         <v/>
       </c>
       <c r="I21" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="22">
@@ -1084,7 +1085,7 @@
         <v/>
       </c>
       <c r="I22" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="23">
@@ -1101,7 +1102,7 @@
         <v>72</v>
       </c>
       <c r="E23" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2" t="str">
         <v/>
@@ -1113,7 +1114,7 @@
         <v/>
       </c>
       <c r="I23" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="24">
@@ -1130,7 +1131,7 @@
         <v>82</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="2" t="str">
         <v/>
@@ -1142,7 +1143,7 @@
         <v/>
       </c>
       <c r="I24" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="25">
@@ -1159,7 +1160,7 @@
         <v>79</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="str">
         <v/>
@@ -1171,7 +1172,7 @@
         <v/>
       </c>
       <c r="I25" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="26">
@@ -1188,7 +1189,7 @@
         <v>94</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="2" t="str">
         <v/>
@@ -1200,7 +1201,7 @@
         <v/>
       </c>
       <c r="I26" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="27">
@@ -1217,7 +1218,7 @@
         <v>60</v>
       </c>
       <c r="E27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
@@ -1229,7 +1230,7 @@
         <v/>
       </c>
       <c r="I27" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="28">
@@ -1246,7 +1247,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
@@ -1258,7 +1259,7 @@
         <v/>
       </c>
       <c r="I28" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="29">
@@ -1275,7 +1276,7 @@
         <v>83</v>
       </c>
       <c r="E29" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="str">
         <v/>
@@ -1287,7 +1288,7 @@
         <v/>
       </c>
       <c r="I29" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="30">
@@ -1304,7 +1305,7 @@
         <v>65</v>
       </c>
       <c r="E30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
@@ -1316,7 +1317,7 @@
         <v/>
       </c>
       <c r="I30" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="31">
@@ -1333,7 +1334,7 @@
         <v>76</v>
       </c>
       <c r="E31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -1345,7 +1346,7 @@
         <v/>
       </c>
       <c r="I31" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="32">
@@ -1374,7 +1375,7 @@
         <v/>
       </c>
       <c r="I32" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="33">
@@ -1391,7 +1392,7 @@
         <v>76</v>
       </c>
       <c r="E33" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="2" t="str">
         <v/>
@@ -1403,7 +1404,7 @@
         <v/>
       </c>
       <c r="I33" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="34">
@@ -1432,7 +1433,7 @@
         <v/>
       </c>
       <c r="I34" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="35">
@@ -1449,7 +1450,7 @@
         <v>87</v>
       </c>
       <c r="E35" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="2" t="str">
         <v/>
@@ -1461,7 +1462,7 @@
         <v/>
       </c>
       <c r="I35" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="36">
@@ -1478,7 +1479,7 @@
         <v>88</v>
       </c>
       <c r="E36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="str">
         <v>✓</v>
@@ -1490,7 +1491,7 @@
         <v/>
       </c>
       <c r="I36" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="37">
@@ -1507,7 +1508,7 @@
         <v>79</v>
       </c>
       <c r="E37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2" t="str">
         <v/>
@@ -1519,7 +1520,7 @@
         <v>✓</v>
       </c>
       <c r="I37" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="38">
@@ -1548,7 +1549,7 @@
         <v/>
       </c>
       <c r="I38" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="39">
@@ -1577,7 +1578,7 @@
         <v/>
       </c>
       <c r="I39" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="40">
@@ -1594,7 +1595,7 @@
         <v>85</v>
       </c>
       <c r="E40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
         <v/>
@@ -1606,7 +1607,7 @@
         <v/>
       </c>
       <c r="I40" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="41">
@@ -1635,7 +1636,7 @@
         <v/>
       </c>
       <c r="I41" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="42">
@@ -1664,7 +1665,7 @@
         <v/>
       </c>
       <c r="I42" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="43">
@@ -1675,13 +1676,13 @@
         <v>Emma Taylor</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
       </c>
       <c r="E43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="2" t="str">
         <v/>
@@ -1693,7 +1694,7 @@
         <v/>
       </c>
       <c r="I43" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="44">
@@ -1710,7 +1711,7 @@
         <v>82</v>
       </c>
       <c r="E44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="str">
         <v/>
@@ -1722,7 +1723,7 @@
         <v/>
       </c>
       <c r="I44" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="45">
@@ -1739,7 +1740,7 @@
         <v>72</v>
       </c>
       <c r="E45" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F45" s="2" t="str">
         <v/>
@@ -1751,7 +1752,7 @@
         <v/>
       </c>
       <c r="I45" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="46">
@@ -1777,10 +1778,10 @@
         <v/>
       </c>
       <c r="H46" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I46" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="47">
@@ -1809,7 +1810,7 @@
         <v/>
       </c>
       <c r="I47" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="48">
@@ -1826,7 +1827,7 @@
         <v>83</v>
       </c>
       <c r="E48" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48" s="2" t="str">
         <v/>
@@ -1838,7 +1839,7 @@
         <v/>
       </c>
       <c r="I48" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="49">
@@ -1855,7 +1856,7 @@
         <v>89</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="str">
         <v/>
@@ -1867,7 +1868,7 @@
         <v/>
       </c>
       <c r="I49" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="50">
@@ -1884,7 +1885,7 @@
         <v>72</v>
       </c>
       <c r="E50" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="str">
         <v/>
@@ -1896,7 +1897,7 @@
         <v/>
       </c>
       <c r="I50" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="51">
@@ -1913,7 +1914,7 @@
         <v>88</v>
       </c>
       <c r="E51" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" s="2" t="str">
         <v/>
@@ -1925,7 +1926,7 @@
         <v/>
       </c>
       <c r="I51" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="52">
@@ -1942,7 +1943,7 @@
         <v>74</v>
       </c>
       <c r="E52" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
         <v>✓</v>
@@ -1954,7 +1955,7 @@
         <v/>
       </c>
       <c r="I52" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="53">
@@ -1983,7 +1984,7 @@
         <v/>
       </c>
       <c r="I53" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="54">
@@ -2000,7 +2001,7 @@
         <v>84</v>
       </c>
       <c r="E54" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="2" t="str">
         <v/>
@@ -2012,7 +2013,7 @@
         <v/>
       </c>
       <c r="I54" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="55">
@@ -2029,7 +2030,7 @@
         <v>88</v>
       </c>
       <c r="E55" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="2" t="str">
         <v/>
@@ -2041,7 +2042,7 @@
         <v/>
       </c>
       <c r="I55" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="56">
@@ -2058,7 +2059,7 @@
         <v>68</v>
       </c>
       <c r="E56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="str">
         <v/>
@@ -2070,7 +2071,7 @@
         <v/>
       </c>
       <c r="I56" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="57">
@@ -2096,10 +2097,10 @@
         <v/>
       </c>
       <c r="H57" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I57" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="58">
@@ -2128,7 +2129,7 @@
         <v/>
       </c>
       <c r="I58" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="59">
@@ -2145,7 +2146,7 @@
         <v>70</v>
       </c>
       <c r="E59" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2" t="str">
         <v>✓</v>
@@ -2154,10 +2155,10 @@
         <v/>
       </c>
       <c r="H59" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I59" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="60">
@@ -2174,7 +2175,7 @@
         <v>82</v>
       </c>
       <c r="E60" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="str">
         <v/>
@@ -2186,7 +2187,7 @@
         <v/>
       </c>
       <c r="I60" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="61">
@@ -2203,7 +2204,7 @@
         <v>74</v>
       </c>
       <c r="E61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="str">
         <v/>
@@ -2215,7 +2216,7 @@
         <v/>
       </c>
       <c r="I61" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="62">
@@ -2232,7 +2233,7 @@
         <v>85</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="2" t="str">
         <v/>
@@ -2244,7 +2245,7 @@
         <v/>
       </c>
       <c r="I62" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="63">
@@ -2261,7 +2262,7 @@
         <v>62</v>
       </c>
       <c r="E63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
         <v/>
@@ -2273,7 +2274,7 @@
         <v/>
       </c>
       <c r="I63" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="64">
@@ -2290,7 +2291,7 @@
         <v>78</v>
       </c>
       <c r="E64" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64" s="2" t="str">
         <v/>
@@ -2302,7 +2303,7 @@
         <v/>
       </c>
       <c r="I64" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="65">
@@ -2319,7 +2320,7 @@
         <v>78</v>
       </c>
       <c r="E65" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
         <v/>
@@ -2331,7 +2332,7 @@
         <v/>
       </c>
       <c r="I65" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="66">
@@ -2348,7 +2349,7 @@
         <v>70</v>
       </c>
       <c r="E66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="str">
         <v>✓</v>
@@ -2360,7 +2361,7 @@
         <v>✓</v>
       </c>
       <c r="I66" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="67">
@@ -2377,7 +2378,7 @@
         <v>70</v>
       </c>
       <c r="E67" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2" t="str">
         <v/>
@@ -2389,7 +2390,7 @@
         <v/>
       </c>
       <c r="I67" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="68">
@@ -2406,7 +2407,7 @@
         <v>77</v>
       </c>
       <c r="E68" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="str">
         <v/>
@@ -2418,7 +2419,7 @@
         <v/>
       </c>
       <c r="I68" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="69">
@@ -2429,13 +2430,13 @@
         <v>Aria Hill</v>
       </c>
       <c r="C69" s="2" t="str">
-        <v>F</v>
+        <v>X</v>
       </c>
       <c r="D69" s="2">
         <v>85</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="str">
         <v/>
@@ -2447,7 +2448,7 @@
         <v/>
       </c>
       <c r="I69" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="70">
@@ -2464,7 +2465,7 @@
         <v>83</v>
       </c>
       <c r="E70" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="2" t="str">
         <v>✓</v>
@@ -2476,7 +2477,7 @@
         <v/>
       </c>
       <c r="I70" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="71">
@@ -2493,7 +2494,7 @@
         <v>83</v>
       </c>
       <c r="E71" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" s="2" t="str">
         <v/>
@@ -2505,7 +2506,7 @@
         <v/>
       </c>
       <c r="I71" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="72">
@@ -2534,7 +2535,7 @@
         <v/>
       </c>
       <c r="I72" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="73">
@@ -2551,7 +2552,7 @@
         <v>73</v>
       </c>
       <c r="E73" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="2" t="str">
         <v/>
@@ -2563,7 +2564,7 @@
         <v/>
       </c>
       <c r="I73" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="74">
@@ -2592,7 +2593,7 @@
         <v/>
       </c>
       <c r="I74" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="75">
@@ -2609,7 +2610,7 @@
         <v>68</v>
       </c>
       <c r="E75" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
         <v/>
@@ -2621,7 +2622,7 @@
         <v/>
       </c>
       <c r="I75" s="2" t="str">
-        <v/>
+        <v>C</v>
       </c>
     </row>
     <row r="76">
@@ -2638,7 +2639,7 @@
         <v>77</v>
       </c>
       <c r="E76" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="str">
         <v/>
@@ -2650,7 +2651,7 @@
         <v/>
       </c>
       <c r="I76" s="2" t="str">
-        <v/>
+        <v>A</v>
       </c>
     </row>
     <row r="77">
@@ -2667,7 +2668,7 @@
         <v>87</v>
       </c>
       <c r="E77" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="str">
         <v/>
@@ -2679,7 +2680,7 @@
         <v/>
       </c>
       <c r="I77" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="78">
@@ -2696,7 +2697,7 @@
         <v>89</v>
       </c>
       <c r="E78" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
         <v/>
@@ -2708,7 +2709,7 @@
         <v/>
       </c>
       <c r="I78" s="2" t="str">
-        <v/>
+        <v>B</v>
       </c>
     </row>
     <row r="79">
@@ -2725,7 +2726,7 @@
         <v>93</v>
       </c>
       <c r="E79" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="2" t="str">
         <v>✓</v>
@@ -2737,7 +2738,7 @@
         <v/>
       </c>
       <c r="I79" s="2" t="str">
-        <v>✓</v>
+        <v>A</v>
       </c>
     </row>
     <row r="80">
@@ -2763,10 +2764,10 @@
         <v/>
       </c>
       <c r="H80" s="2" t="str">
-        <v/>
+        <v>✓</v>
       </c>
       <c r="I80" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="81">
@@ -2795,7 +2796,7 @@
         <v/>
       </c>
       <c r="I81" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
     <row r="82">
@@ -2824,7 +2825,7 @@
         <v/>
       </c>
       <c r="I82" s="2" t="str">
-        <v/>
+        <v>D</v>
       </c>
     </row>
   </sheetData>
@@ -2924,4 +2925,103 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>Attribute</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>Options</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>Gender</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>F</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>M</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <v>X</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>Reading score</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Number</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>Math level</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Scale</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>Learning support</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>English support</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>Leadership</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>Checkbox</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>Previous class</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>List</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>C</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <v>D</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+  </ignoredErrors>
+</worksheet>
 </file>